--- a/data/output/seo_search_results.xlsx
+++ b/data/output/seo_search_results.xlsx
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="Q16" s="17" t="n">
-        <v>0.7942585127662037</v>
+        <v>0.7942585185185186</v>
       </c>
       <c r="R16" s="10" t="inlineStr">
         <is>
@@ -1410,23 +1410,89 @@
       <c r="A17" s="16" t="n">
         <v>46063</v>
       </c>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="n"/>
-      <c r="F17" s="10" t="n"/>
-      <c r="G17" s="10" t="n"/>
-      <c r="H17" s="10" t="n"/>
-      <c r="I17" s="10" t="n"/>
-      <c r="J17" s="10" t="n"/>
-      <c r="K17" s="10" t="n"/>
-      <c r="L17" s="10" t="n"/>
-      <c r="M17" s="10" t="n"/>
-      <c r="N17" s="10" t="n"/>
-      <c r="O17" s="10" t="n"/>
-      <c r="P17" s="10" t="n"/>
-      <c r="Q17" s="10" t="n"/>
-      <c r="R17" s="10" t="n"/>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>14/P.1</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>2/P.1</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>3/P.1</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>12/P.1</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>13/P.1</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>12/P.1</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>4/P.1</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>7/P.1</t>
+        </is>
+      </c>
+      <c r="J17" s="10" t="inlineStr">
+        <is>
+          <t>14/P.2</t>
+        </is>
+      </c>
+      <c r="K17" s="10" t="inlineStr">
+        <is>
+          <t>3/P.1</t>
+        </is>
+      </c>
+      <c r="L17" s="10" t="inlineStr">
+        <is>
+          <t>4/P.1</t>
+        </is>
+      </c>
+      <c r="M17" s="10" t="inlineStr">
+        <is>
+          <t>5/P.1</t>
+        </is>
+      </c>
+      <c r="N17" s="10" t="inlineStr">
+        <is>
+          <t>1/P.1</t>
+        </is>
+      </c>
+      <c r="O17" s="10" t="inlineStr">
+        <is>
+          <t>7/P.1</t>
+        </is>
+      </c>
+      <c r="P17" s="10" t="inlineStr">
+        <is>
+          <t>2/P.1</t>
+        </is>
+      </c>
+      <c r="Q17" s="17" t="n">
+        <v>0.7200783113541667</v>
+      </c>
+      <c r="R17" s="10" t="inlineStr">
+        <is>
+          <t>1/P.1</t>
+        </is>
+      </c>
       <c r="S17" s="10" t="n"/>
     </row>
     <row r="18">
